--- a/survey_templates/041_student_reflection_form--survey_templates.xlsx
+++ b/survey_templates/041_student_reflection_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1573,29 +1573,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>physical_education</t>
+          <t>drama</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Physical Education</t>
+          <t>Drama</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>current_subjects_choices</t>
+          <t>submission_time_zone_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>drama</t>
+          <t>est</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Drama</t>
+          <t>EST</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>est</t>
+          <t>cst</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>EST</t>
+          <t>CST</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>cst</t>
+          <t>mst</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CST</t>
+          <t>MST</t>
         </is>
       </c>
     </row>
@@ -1641,29 +1641,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>mst</t>
+          <t>pst</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MST</t>
+          <t>PST</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>submission_time_zone_choices</t>
+          <t>student_reflection_status_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>pst</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PST</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>not_started</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1709,29 +1709,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>completed_with_comments</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Completed with Comments</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>student_reflection_status_choices</t>
+          <t>teacher_reflection_status_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>completed_with_comments</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Completed with Comments</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>not_started</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1777,29 +1777,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>completed_with_comments</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Completed with Comments</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>teacher_reflection_status_choices</t>
+          <t>submission_status_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>completed_with_comments</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Completed with Comments</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>approved</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Rejected</t>
         </is>
       </c>
     </row>
@@ -1828,29 +1828,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>submission_status_choices</t>
+          <t>submission_time_zone_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>est</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>EST</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>est</t>
+          <t>cst</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>EST</t>
+          <t>CST</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>cst</t>
+          <t>mst</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CST</t>
+          <t>MST</t>
         </is>
       </c>
     </row>
@@ -1896,27 +1896,10 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>mst</t>
+          <t>pst</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
-        <is>
-          <t>MST</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>submission_time_zone_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>pst</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
         <is>
           <t>PST</t>
         </is>
